--- a/sample_data/calendar.xlsx
+++ b/sample_data/calendar.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -448,59 +448,1184 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46037</v>
+        <v>45292</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>キックオフMTG</t>
+          <t>元日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>全社キックオフ</t>
+          <t>公休（日本の祝日）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46096</v>
+        <v>45299</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Designレビュー</t>
+          <t>成人の日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>中間レビュー+意思決定</t>
+          <t>公休（日本の祝日）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46132</v>
+        <v>45333</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>リリース判定会議</t>
+          <t>建国記念の日</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Goサインの有無確認</t>
+          <t>公休（日本の祝日）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
+        <v>45334</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45345</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45371</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45411</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45415</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>憲法記念日</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45416</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>みどりの日</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45417</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45418</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45488</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45515</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45516</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45551</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45557</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45558</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45579</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45599</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45600</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45711</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45736</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45776</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45780</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>憲法記念日</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45781</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>みどりの日</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45782</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>憲法記念日</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>みどりの日</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>国民の休日</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46349</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46398</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46429</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46441</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46467</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46468</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>振替休日</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46506</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46510</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>憲法記念日</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46511</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>みどりの日</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46512</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46587</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46610</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46650</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46653</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46671</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46694</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46714</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>キックオフMTG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>全社キックオフ</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Designレビュー</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>中間レビュー+意思決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>リリース判定会議</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Goサインの有無確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>ポストモーテム</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>品質振り返り</t>
         </is>

--- a/sample_data/calendar.xlsx
+++ b/sample_data/calendar.xlsx
@@ -421,26 +421,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日付</t>
+          <t>開始日</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>終了日</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
@@ -450,12 +456,15 @@
       <c r="A2" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>元日</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -465,12 +474,15 @@
       <c r="A3" s="2" t="n">
         <v>45299</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="n">
+        <v>45299</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>成人の日</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -480,12 +492,15 @@
       <c r="A4" s="2" t="n">
         <v>45333</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>建国記念の日</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>45334</v>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t>建国記念の日・振替休日</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -493,14 +508,17 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45334</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>45345</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45345</v>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -508,14 +526,17 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45345</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>天皇誕生日</t>
-        </is>
+        <v>45371</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45371</v>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -523,14 +544,17 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45371</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>春分の日</t>
-        </is>
+        <v>45411</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45411</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -538,14 +562,17 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45411</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>昭和の日</t>
-        </is>
+        <v>45415</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45418</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>憲法記念日・みどりの日・こどもの日・振替休日</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -553,14 +580,17 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45415</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>憲法記念日</t>
-        </is>
+        <v>45488</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45488</v>
       </c>
       <c r="C9" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -568,14 +598,17 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45416</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>みどりの日</t>
-        </is>
+        <v>45515</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45516</v>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t>山の日・振替休日</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -583,14 +616,17 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45417</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>こどもの日</t>
-        </is>
+        <v>45551</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551</v>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -598,14 +634,17 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45418</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>45557</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45558</v>
       </c>
       <c r="C12" t="inlineStr">
+        <is>
+          <t>秋分の日・振替休日</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -613,14 +652,17 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45488</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>海の日</t>
-        </is>
+        <v>45579</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45579</v>
       </c>
       <c r="C13" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -628,14 +670,17 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45515</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>山の日</t>
-        </is>
+        <v>45599</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45600</v>
       </c>
       <c r="C14" t="inlineStr">
+        <is>
+          <t>文化の日・振替休日</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -643,14 +688,17 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45516</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>45619</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619</v>
       </c>
       <c r="C15" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -658,14 +706,17 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45551</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>敬老の日</t>
-        </is>
+        <v>45658</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45658</v>
       </c>
       <c r="C16" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -673,14 +724,17 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45557</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>秋分の日</t>
-        </is>
+        <v>45670</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45670</v>
       </c>
       <c r="C17" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -688,14 +742,17 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45558</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>45699</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45699</v>
       </c>
       <c r="C18" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -703,14 +760,17 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45579</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>スポーツの日</t>
-        </is>
+        <v>45711</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45712</v>
       </c>
       <c r="C19" t="inlineStr">
+        <is>
+          <t>天皇誕生日・振替休日</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -718,14 +778,17 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45599</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>文化の日</t>
-        </is>
+        <v>45736</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45736</v>
       </c>
       <c r="C20" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -733,14 +796,17 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45600</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>45776</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45776</v>
       </c>
       <c r="C21" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -748,14 +814,17 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45619</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>勤労感謝の日</t>
-        </is>
+        <v>45780</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45783</v>
       </c>
       <c r="C22" t="inlineStr">
+        <is>
+          <t>憲法記念日・みどりの日・こどもの日・振替休日</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -763,14 +832,17 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>元日</t>
-        </is>
+        <v>45859</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45859</v>
       </c>
       <c r="C23" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -778,14 +850,17 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45670</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>成人の日</t>
-        </is>
+        <v>45880</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45880</v>
       </c>
       <c r="C24" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -793,14 +868,17 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>建国記念の日</t>
-        </is>
+        <v>45915</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45915</v>
       </c>
       <c r="C25" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -808,14 +886,17 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>天皇誕生日</t>
-        </is>
+        <v>45923</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45923</v>
       </c>
       <c r="C26" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -823,14 +904,17 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>45943</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45943</v>
       </c>
       <c r="C27" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -838,14 +922,17 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45736</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>春分の日</t>
-        </is>
+        <v>45964</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45964</v>
       </c>
       <c r="C28" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -853,14 +940,17 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>昭和の日</t>
-        </is>
+        <v>45984</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45985</v>
       </c>
       <c r="C29" t="inlineStr">
+        <is>
+          <t>勤労感謝の日・振替休日</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -868,14 +958,17 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45780</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>憲法記念日</t>
-        </is>
+        <v>46023</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46023</v>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -883,14 +976,17 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45781</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>みどりの日</t>
-        </is>
+        <v>46034</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46034</v>
       </c>
       <c r="C31" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -898,14 +994,17 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45782</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>こどもの日</t>
-        </is>
+        <v>46064</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46064</v>
       </c>
       <c r="C32" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -913,14 +1012,17 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45783</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>46076</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46076</v>
       </c>
       <c r="C33" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -928,14 +1030,17 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45859</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>海の日</t>
-        </is>
+        <v>46101</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46101</v>
       </c>
       <c r="C34" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -943,14 +1048,17 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45880</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>山の日</t>
-        </is>
+        <v>46141</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46141</v>
       </c>
       <c r="C35" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -958,14 +1066,17 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45915</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>敬老の日</t>
-        </is>
+        <v>46145</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46148</v>
       </c>
       <c r="C36" t="inlineStr">
+        <is>
+          <t>憲法記念日・みどりの日・こどもの日・振替休日</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -973,14 +1084,17 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45923</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>秋分の日</t>
-        </is>
+        <v>46223</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46223</v>
       </c>
       <c r="C37" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -988,14 +1102,17 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45943</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>スポーツの日</t>
-        </is>
+        <v>46245</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46245</v>
       </c>
       <c r="C38" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1003,14 +1120,17 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45964</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>文化の日</t>
-        </is>
+        <v>46286</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46288</v>
       </c>
       <c r="C39" t="inlineStr">
+        <is>
+          <t>敬老の日・国民の休日・秋分の日</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1018,14 +1138,17 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>勤労感謝の日</t>
-        </is>
+        <v>46307</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46307</v>
       </c>
       <c r="C40" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1033,14 +1156,17 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45985</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>46329</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46329</v>
       </c>
       <c r="C41" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1048,14 +1174,17 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>元日</t>
-        </is>
+        <v>46349</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46349</v>
       </c>
       <c r="C42" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1063,14 +1192,17 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>成人の日</t>
-        </is>
+        <v>46388</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46388</v>
       </c>
       <c r="C43" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1078,14 +1210,17 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46064</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>建国記念の日</t>
-        </is>
+        <v>46398</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46398</v>
       </c>
       <c r="C44" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1093,14 +1228,17 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46076</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>天皇誕生日</t>
-        </is>
+        <v>46429</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46429</v>
       </c>
       <c r="C45" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1108,14 +1246,17 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>春分の日</t>
-        </is>
+        <v>46441</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46441</v>
       </c>
       <c r="C46" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1123,14 +1264,17 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46141</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>昭和の日</t>
-        </is>
+        <v>46467</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46468</v>
       </c>
       <c r="C47" t="inlineStr">
+        <is>
+          <t>春分の日・振替休日</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1138,14 +1282,17 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46145</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>憲法記念日</t>
-        </is>
+        <v>46506</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>46506</v>
       </c>
       <c r="C48" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1153,14 +1300,17 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>みどりの日</t>
-        </is>
+        <v>46510</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>46512</v>
       </c>
       <c r="C49" t="inlineStr">
+        <is>
+          <t>憲法記念日・みどりの日・こどもの日</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1168,14 +1318,17 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>こどもの日</t>
-        </is>
+        <v>46587</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>46587</v>
       </c>
       <c r="C50" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1183,14 +1336,17 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
+        <v>46610</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>46610</v>
       </c>
       <c r="C51" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1198,14 +1354,17 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>海の日</t>
-        </is>
+        <v>46650</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>46650</v>
       </c>
       <c r="C52" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1213,14 +1372,17 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>山の日</t>
-        </is>
+        <v>46653</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>46653</v>
       </c>
       <c r="C53" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1228,14 +1390,17 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>敬老の日</t>
-        </is>
+        <v>46671</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>46671</v>
       </c>
       <c r="C54" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1243,14 +1408,17 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>国民の休日</t>
-        </is>
+        <v>46694</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>46694</v>
       </c>
       <c r="C55" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>公休（日本の祝日）</t>
         </is>
@@ -1258,376 +1426,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>秋分の日</t>
-        </is>
+        <v>46714</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>46714</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>スポーツの日</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>文化の日</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>46349</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
           <t>勤労感謝の日</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>46388</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>元日</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>46398</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>成人の日</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>46429</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>建国記念の日</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>46441</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>天皇誕生日</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>46467</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>春分の日</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>46468</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>振替休日</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46506</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>昭和の日</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46510</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>憲法記念日</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>46511</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>みどりの日</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>46512</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>こどもの日</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>46587</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>海の日</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>46610</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>山の日</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>46650</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>敬老の日</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>46653</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>秋分の日</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>46671</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>スポーツの日</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>46694</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>文化の日</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>46714</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>勤労感謝の日</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>公休（日本の祝日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>46037</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>キックオフMTG</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>全社キックオフ</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Designレビュー</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>中間レビュー+意思決定</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>46132</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>リリース判定会議</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Goサインの有無確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ポストモーテム</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>品質振り返り</t>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>公休（日本の祝日）</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1673,114 +1484,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>田中</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>46063</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>有給</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>佐藤</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>46083</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46083</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>半休</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>鈴木</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>46139</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>連休+有給</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>高橋</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>夏季休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>小林</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46104</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>46104</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>通院</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>渡辺</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>私用</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/calendar.xlsx
+++ b/sample_data/calendar.xlsx
@@ -10,8 +10,16 @@
     <sheet name="イベント" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="祝日・休日" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="非稼働日" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="テスト" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="設定" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="tt_list">OFFSET(設定!$A$2,0,0,COUNTA(設定!$A$2:$A$1000),1)</definedName>
+    <definedName name="asg_list">OFFSET(設定!$B$2,0,0,COUNTA(設定!$B$2:$B$1000),1)</definedName>
+    <definedName name="st_list">OFFSET(設定!$C$2,0,0,COUNTA(設定!$C$2:$C$1000),1)</definedName>
+    <definedName name="res_list">OFFSET(設定!$D$2,0,0,COUNTA(設定!$D$2:$D$1000),1)</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'テスト'!$A$1:$Q$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,16 +40,35 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,14 +76,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2234,4 +2294,1200 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>機能ID</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>機能名称</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>連携方向</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>送受</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>テスト種別</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>テストID</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>テスト名</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>テスト概要</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>予定開始</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>予定終了</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>実開始日</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>実終了日</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>テスト状況</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備）</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備） 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>SYM04040</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>M-BOM外部テーブル連携</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>SYM04040-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>M-BOM外部テーブル連携 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>送受PM原文に明記なし=要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>受・WindchillDB内</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>受機能：受ファイル準備方法の調整要</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SYM01010</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>BOM-BOP EES</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>local/global</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>SYM01010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>BOM-BOP EES 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>送受PM原文に明記なし=要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>★6/15までに目的データでストーリー疎通</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>単体</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-単体-01</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 単体</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>（テスト概要をここに記載）</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>（入力例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>結合</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-結合-01</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 結合</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>（テスト概要をここに記載）</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>（入力例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-E2E-01</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 E2E</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>（テスト概要をここに記載）</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>（入力例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>デモ</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-デモ-01</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 デモ</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>（テスト概要をここに記載）</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>（入力例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SY64010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>メーカーファイル連携（送）</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>global/local</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>SY64010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>メーカーファイル連携（送） 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>SY65020</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>フロアストック区分連携（受）</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>SY65020-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>フロアストック区分連携（受） 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>受機能：受ファイル準備方法の調整要</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SY26010</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>主要選定区分取り込み機能</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>SY26010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>主要選定区分取り込み機能 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>送受PM原文に明記なし=要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>SY65010</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>BPA・COST受信（受信）</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>SY65010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>BPA・COST受信（受信） 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>受機能：受ファイル準備方法の調整要</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SY24010</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>取引先IF連携</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>SY24010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>取引先IF連携 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>送受PM原文に明記なし=要確認</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q15"/>
+  <dataValidations count="4">
+    <dataValidation sqref="F2:F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=tt_list</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=asg_list</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=st_list</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=res_list</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>テスト種別</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>← この列に行を足す/消すだけでドロップダウンに反映されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>単体</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>浜下</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>結合</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>成瀬</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>吉野</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>野口</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>課題発生中</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W2W</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>デモ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sample_data/calendar.xlsx
+++ b/sample_data/calendar.xlsx
@@ -18,7 +18,7 @@
     <definedName name="asg_list">OFFSET(設定!$B$2,0,0,COUNTA(設定!$B$2:$B$1000),1)</definedName>
     <definedName name="st_list">OFFSET(設定!$C$2,0,0,COUNTA(設定!$C$2:$C$1000),1)</definedName>
     <definedName name="res_list">OFFSET(設定!$D$2,0,0,COUNTA(設定!$D$2:$D$1000),1)</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'テスト'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'テスト'!$A$1:$Q$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2302,7 +2302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2321,7 +2321,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2417,24 +2417,20 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>SYM04010</t>
+          <t>SY24010</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>グローバル列マスタ出力（送備）</t>
+          <t>取引先IF連携</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>送</t>
-        </is>
-      </c>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>簡易疎通</t>
@@ -2442,12 +2438,12 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>SYM04010-簡易疎通-01</t>
+          <t>SY24010-簡易疎通-01</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>グローバル列マスタ出力（送備） 簡易疎通</t>
+          <t>取引先IF連携 簡易疎通</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -2474,7 +2470,11 @@
         </is>
       </c>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="5" t="n"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>送受PM原文に明記なし=要確認</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SYM04040</t>
+          <t>SY26010</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>M-BOM外部テーブル連携</t>
+          <t>主要選定区分取り込み機能</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>global</t>
         </is>
       </c>
       <c r="E3" s="4" t="n"/>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>SYM04040-簡易疎通-01</t>
+          <t>SY26010-簡易疎通-01</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>M-BOM外部テーブル連携 簡易疎通</t>
+          <t>主要選定区分取り込み機能 簡易疎通</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -2542,73 +2542,69 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>SYM05020</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>外部列挙マスタ受</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>受・WindchillDB内</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>受</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SY64010</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>メーカーファイル連携（送）</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>global/local</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>簡易疎通</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>SYM05020-簡易疎通-01</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>外部列挙マスタ受 簡易疎通</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>SY64010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>メーカーファイル連携（送） 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>global/local middleware への疎通連携確認</t>
         </is>
       </c>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>受機能：受ファイル準備方法の調整要</t>
-        </is>
-      </c>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2616,49 +2612,57 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SYM01010</t>
+          <t>SY64010</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>BOM-BOP EES</t>
+          <t>メーカーファイル連携（送）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>local/global</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
+          <t>global/local</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>簡易疎通</t>
+          <t>結合</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>SYM01010-簡易疎通-01</t>
+          <t>SY64010-結合-01</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>BOM-BOP EES 簡易疎通</t>
+          <t>メーカーファイル連携（送） 結合</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>global/local middleware への疎通連携確認</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n"/>
+          <t>メーカーファイル送信の結合</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>成瀬</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="M5" s="4" t="n"/>
@@ -2671,7 +2675,7 @@
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>送受PM原文に明記なし=要確認</t>
+          <t>（デモ用サンプル）</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2685,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>SYM02010</t>
+          <t>SY65010</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信</t>
+          <t>BPA・COST受信（受信）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2701,46 +2705,62 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>簡易疎通</t>
+          <t>単体</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>SYM02010-簡易疎通-01</t>
+          <t>SY65010-単体-01</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信 簡易疎通</t>
+          <t>BPA・COST受信（受信） 単体</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>global/local middleware への疎通連携確認</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n"/>
+          <t>コスト受信の単体。項目欠落の課題</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>野口</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="n"/>
+          <t>課題発生中</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>★6/15までに目的データでストーリー疎通</t>
+          <t>（デモ用サンプル）</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2770,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>SYM02010</t>
+          <t>SY65010</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信</t>
+          <t>BPA・COST受信（受信）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -2770,27 +2790,35 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>単体</t>
+          <t>簡易疎通</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>SYM02010-単体-01</t>
+          <t>SY65010-簡易疎通-01</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信 単体</t>
+          <t>BPA・COST受信（受信） 簡易疎通</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>（テスト概要をここに記載）</t>
+          <t>global/local middleware への疎通連携確認</t>
         </is>
       </c>
       <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
       <c r="O7" s="6" t="inlineStr">
@@ -2801,7 +2829,7 @@
       <c r="P7" s="6" t="n"/>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>（入力例）</t>
+          <t>受機能：受ファイル準備方法の調整要</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2839,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>SYM02010</t>
+          <t>SY65010</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信</t>
+          <t>BPA・COST受信（受信）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2831,27 +2859,39 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>W2W</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>SYM02010-結合-01</t>
+          <t>SY65010-W2W-01</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信 結合</t>
+          <t>BPA・COST受信（受信） W2W</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>（テスト概要をここに記載）</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+          <t>BPA/COST の W2W 連携</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>浜下</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
       <c r="O8" s="6" t="inlineStr">
@@ -2862,7 +2902,7 @@
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>（入力例）</t>
+          <t>（デモ用サンプル）</t>
         </is>
       </c>
     </row>
@@ -2872,17 +2912,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>SYM02010</t>
+          <t>SY65020</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信</t>
+          <t>フロアストック区分連携（受）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2892,38 +2932,62 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>E2E</t>
+          <t>単体</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>SYM02010-E2E-01</t>
+          <t>SY65020-単体-01</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信 E2E</t>
+          <t>フロアストック区分連携（受） 単体</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>（テスト概要をここに記載）</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
+          <t>区分受信の単体確認</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>吉野</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="n"/>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>（入力例）</t>
+          <t>（デモ用サンプル）</t>
         </is>
       </c>
     </row>
@@ -2933,17 +2997,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>SYM02010</t>
+          <t>SY65020</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信</t>
+          <t>フロアストック区分連携（受）</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2953,27 +3017,35 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>デモ</t>
+          <t>簡易疎通</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>SYM02010-デモ-01</t>
+          <t>SY65020-簡易疎通-01</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>CID情報受信 デモ</t>
+          <t>フロアストック区分連携（受） 簡易疎通</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>（テスト概要をここに記載）</t>
+          <t>global/local middleware への疎通連携確認</t>
         </is>
       </c>
       <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="6" t="inlineStr">
@@ -2984,7 +3056,7 @@
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>（入力例）</t>
+          <t>受機能：受ファイル準備方法の調整要</t>
         </is>
       </c>
     </row>
@@ -2994,24 +3066,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SY64010</t>
+          <t>SYM01010</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>メーカーファイル連携（送）</t>
+          <t>BOM-BOP EES</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>global/local</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>送</t>
-        </is>
-      </c>
+          <t>local/global</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>簡易疎通</t>
@@ -3019,12 +3087,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>SY64010-簡易疎通-01</t>
+          <t>SYM01010-簡易疎通-01</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>メーカーファイル連携（送） 簡易疎通</t>
+          <t>BOM-BOP EES 簡易疎通</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -3051,7 +3119,11 @@
         </is>
       </c>
       <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="5" t="n"/>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>送受PM原文に明記なし=要確認</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -3059,17 +3131,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>SY65020</t>
+          <t>SYM02010</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>フロアストック区分連携（受）</t>
+          <t>CID情報受信</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>global</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -3079,111 +3151,147 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>簡易疎通</t>
+          <t>単体</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>SY65020-簡易疎通-01</t>
+          <t>SYM02010-単体-01</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>フロアストック区分連携（受） 簡易疎通</t>
+          <t>CID情報受信 単体</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>global/local middleware への疎通連携確認</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="n"/>
+          <t>CID受信ロジックの単体確認</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>浜下</t>
+        </is>
+      </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="n"/>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>受機能：受ファイル準備方法の調整要</t>
+          <t>（デモ用サンプル）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>SY26010</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>主要選定区分取り込み機能</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>global</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>簡易疎通</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>SY26010-簡易疎通-01</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>主要選定区分取り込み機能 簡易疎通</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>global/local middleware への疎通連携確認</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>送受PM原文に明記なし=要確認</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>結合</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-結合-01</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 結合</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>global連携の結合。データ不整合の課題</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>成瀬</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>課題発生中</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3301,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>SY65010</t>
+          <t>SYM02010</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>BPA・COST受信（受信）</t>
+          <t>CID情報受信</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -3218,12 +3326,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>SY65010-簡易疎通-01</t>
+          <t>SYM02010-簡易疎通-01</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>BPA・COST受信（受信） 簡易疎通</t>
+          <t>CID情報受信 簡易疎通</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -3239,7 +3347,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M14" s="6" t="n"/>
@@ -3252,88 +3360,834 @@
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="7" t="inlineStr">
         <is>
+          <t>★6/15までに目的データでストーリー疎通</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>W2W</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-W2W-01</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 W2W</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Windchill間 W2W 連携確認</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>吉野</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-E2E-01</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 E2E</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>目的データでストーリー疎通(E2E)</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>野口</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>デモ</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>SYM02010-デモ-01</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>CID情報受信 デモ</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>顧客向けデモ</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>浜下</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備）</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>単体</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010-単体-01</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備） 単体</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>出力ロジックの単体確認</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>成瀬</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備）</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備） 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備）</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>SYM04010-手順-01</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>グローバル列マスタ出力（送備） 手順</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>運用手順テスト</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>成瀬</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>SYM04040</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>M-BOM外部テーブル連携</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>SYM04040-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>M-BOM外部テーブル連携 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>送受PM原文に明記なし=要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>受・WindchillDB内</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>単体</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020-単体-01</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受 単体</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>受信ロジックの単体確認</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>吉野</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>受・WindchillDB内</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>結合</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020-結合-01</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受 結合</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>WindchillDB内取込の結合(実施中)</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>吉野</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>受・WindchillDB内</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>簡易疎通</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020-簡易疎通-01</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受 簡易疎通</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>global/local middleware への疎通連携確認</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
           <t>受機能：受ファイル準備方法の調整要</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>SY24010</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>取引先IF連携</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>簡易疎通</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>SY24010-簡易疎通-01</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>取引先IF連携 簡易疎通</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>global/local middleware への疎通連携確認</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>受・WindchillDB内</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>受</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>SYM05020-E2E-01</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>外部列挙マスタ受 E2E</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>受領→反映のE2E</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>野口</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>送受PM原文に明記なし=要確認</t>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>（デモ用サンプル）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q15"/>
+  <autoFilter ref="A1:Q25"/>
   <dataValidations count="4">
-    <dataValidation sqref="F2:F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=tt_list</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=asg_list</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=st_list</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=res_list</formula1>
     </dataValidation>
   </dataValidations>
